--- a/xls/patchtest_16.xlsx
+++ b/xls/patchtest_16.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="new_sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr fullCalcOnLoad="1" calcMode="auto"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="13">
   <si>
     <t>type w</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>PiecewisePolynomial{:Quadratic2D}</t>
+  </si>
+  <si>
+    <t>Inf</t>
   </si>
 </sst>
 </file>
@@ -448,899 +451,899 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>9</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>289</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2">
-        <v>3072</v>
-      </c>
-      <c r="G2">
-        <v>-12.3216856979967</v>
-      </c>
-      <c r="H2">
-        <v>-11.730148748483925</v>
-      </c>
-      <c r="I2">
-        <v>Inf</v>
+      <c r="F2" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-11.355355873445122</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-10.797652500910424</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>289</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F3">
-        <v>3072</v>
-      </c>
-      <c r="G3">
-        <v>-11.451916070432516</v>
-      </c>
-      <c r="H3">
-        <v>-10.655975870920841</v>
-      </c>
-      <c r="I3">
-        <v>Inf</v>
+      <c r="F3" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-11.112120225452726</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-10.421651697043695</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>25</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>289</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="F4">
-        <v>3072</v>
-      </c>
-      <c r="G4">
-        <v>-11.464154954696989</v>
-      </c>
-      <c r="H4">
-        <v>-10.591904055656919</v>
-      </c>
-      <c r="I4">
-        <v>Inf</v>
+      <c r="F4" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-10.92833083167661</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-10.060709115161467</v>
+      </c>
+      <c r="I4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>36</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>289</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
-      <c r="F5">
-        <v>3072</v>
-      </c>
-      <c r="G5">
-        <v>-11.232650217713143</v>
-      </c>
-      <c r="H5">
-        <v>-10.264520034507376</v>
-      </c>
-      <c r="I5">
-        <v>Inf</v>
+      <c r="F5" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-11.25225533626782</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-10.260757258961105</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>49</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>289</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
-      <c r="F6">
-        <v>3072</v>
-      </c>
-      <c r="G6">
-        <v>-11.299584826794977</v>
-      </c>
-      <c r="H6">
-        <v>-10.245448237234228</v>
-      </c>
-      <c r="I6">
-        <v>Inf</v>
+      <c r="F6" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-10.595508799575914</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-9.811977189380842</v>
+      </c>
+      <c r="I6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>64</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>289</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
-      <c r="F7">
-        <v>3072</v>
-      </c>
-      <c r="G7">
-        <v>-11.036286288952008</v>
-      </c>
-      <c r="H7">
-        <v>-10.19567955452125</v>
-      </c>
-      <c r="I7">
-        <v>Inf</v>
+      <c r="F7" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-11.11579813080697</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-10.112143043352363</v>
+      </c>
+      <c r="I7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>81</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>289</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
-      <c r="F8">
-        <v>3072</v>
-      </c>
-      <c r="G8">
-        <v>-11.361339095083531</v>
-      </c>
-      <c r="H8">
-        <v>-10.355458668300079</v>
-      </c>
-      <c r="I8">
-        <v>Inf</v>
+      <c r="F8" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-11.044370244161811</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-10.202729060588673</v>
+      </c>
+      <c r="I8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>100</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>289</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
-      <c r="F9">
-        <v>3072</v>
-      </c>
-      <c r="G9">
-        <v>-11.380259021855458</v>
-      </c>
-      <c r="H9">
-        <v>-10.297500611614396</v>
-      </c>
-      <c r="I9">
-        <v>Inf</v>
+      <c r="F9" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-10.895551365742053</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-10.047127388495744</v>
+      </c>
+      <c r="I9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>121</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>289</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
-      <c r="F10">
-        <v>3072</v>
-      </c>
-      <c r="G10">
-        <v>-10.971996355746441</v>
-      </c>
-      <c r="H10">
-        <v>-10.095169136313178</v>
-      </c>
-      <c r="I10">
-        <v>Inf</v>
+      <c r="F10" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-11.020248090444863</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-10.089508806671521</v>
+      </c>
+      <c r="I10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>144</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>289</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
-      <c r="F11">
-        <v>3072</v>
-      </c>
-      <c r="G11">
-        <v>-10.727736496167317</v>
-      </c>
-      <c r="H11">
-        <v>-9.93219775890314</v>
-      </c>
-      <c r="I11">
-        <v>Inf</v>
+      <c r="F11" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-10.832192395319614</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-9.911701903163612</v>
+      </c>
+      <c r="I11" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>9</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>169</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>289</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
-      <c r="F12">
-        <v>3072</v>
-      </c>
-      <c r="G12">
-        <v>-10.98891296025522</v>
-      </c>
-      <c r="H12">
-        <v>-10.007294616886615</v>
-      </c>
-      <c r="I12">
-        <v>Inf</v>
+      <c r="F12" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-11.025189803684004</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-10.022672329153108</v>
+      </c>
+      <c r="I12" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>196</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>289</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
-      <c r="F13">
-        <v>3072</v>
-      </c>
-      <c r="G13">
-        <v>-11.079701463563943</v>
-      </c>
-      <c r="H13">
-        <v>-9.960216877605507</v>
-      </c>
-      <c r="I13">
-        <v>Inf</v>
+      <c r="F13" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-10.717086771596184</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-9.76268751973744</v>
+      </c>
+      <c r="I13" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>9</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>225</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>289</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
-      <c r="F14">
-        <v>3072</v>
-      </c>
-      <c r="G14">
-        <v>-11.125420997667456</v>
-      </c>
-      <c r="H14">
-        <v>-10.046269981487113</v>
-      </c>
-      <c r="I14">
-        <v>Inf</v>
+      <c r="F14" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-10.586072955012378</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-9.856828758911808</v>
+      </c>
+      <c r="I14" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>9</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>256</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>289</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
-      <c r="F15">
-        <v>3072</v>
-      </c>
-      <c r="G15">
-        <v>-10.718739055120391</v>
-      </c>
-      <c r="H15">
-        <v>-9.811893630183478</v>
-      </c>
-      <c r="I15">
-        <v>Inf</v>
+      <c r="F15" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-10.698423379670974</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-9.740186555244563</v>
+      </c>
+      <c r="I15" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>9</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>289</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>289</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
-      <c r="F16">
-        <v>3072</v>
-      </c>
-      <c r="G16">
-        <v>-11.065764389852024</v>
-      </c>
-      <c r="H16">
-        <v>-10.041524795519203</v>
-      </c>
-      <c r="I16">
-        <v>Inf</v>
+      <c r="F16" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-11.032942708399721</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-10.071352028057817</v>
+      </c>
+      <c r="I16" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>9</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>324</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>289</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
       </c>
-      <c r="F17">
-        <v>3072</v>
-      </c>
-      <c r="G17">
-        <v>-10.288114496644308</v>
-      </c>
-      <c r="H17">
-        <v>-9.533305268625167</v>
-      </c>
-      <c r="I17">
-        <v>Inf</v>
+      <c r="F17" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-10.789600378784051</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-9.7305430758519</v>
+      </c>
+      <c r="I17" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>9</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="n">
         <v>361</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>289</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
       </c>
-      <c r="F18">
-        <v>3072</v>
-      </c>
-      <c r="G18">
-        <v>-10.182751673948212</v>
-      </c>
-      <c r="H18">
-        <v>-9.403687490689881</v>
-      </c>
-      <c r="I18">
-        <v>Inf</v>
+      <c r="F18" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-10.225310061863997</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-9.460285712212892</v>
+      </c>
+      <c r="I18" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>9</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>400</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>289</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
       </c>
-      <c r="F19">
-        <v>3072</v>
-      </c>
-      <c r="G19">
-        <v>-10.613345688196443</v>
-      </c>
-      <c r="H19">
-        <v>-9.520315267475034</v>
-      </c>
-      <c r="I19">
-        <v>Inf</v>
+      <c r="F19" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-10.354225459836744</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-9.581535683943937</v>
+      </c>
+      <c r="I19" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>9</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="n">
         <v>441</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>289</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
       </c>
-      <c r="F20">
-        <v>3072</v>
-      </c>
-      <c r="G20">
-        <v>-10.47621856020318</v>
-      </c>
-      <c r="H20">
-        <v>-9.466908147585217</v>
-      </c>
-      <c r="I20">
-        <v>Inf</v>
+      <c r="F20" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-10.234670200264517</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-9.49620266142147</v>
+      </c>
+      <c r="I20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>9</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="n">
         <v>484</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>289</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
       </c>
-      <c r="F21">
-        <v>3072</v>
-      </c>
-      <c r="G21">
-        <v>-10.126274645600429</v>
-      </c>
-      <c r="H21">
-        <v>-9.296531983085224</v>
-      </c>
-      <c r="I21">
-        <v>Inf</v>
+      <c r="F21" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-10.409813669810204</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-9.434172120097957</v>
+      </c>
+      <c r="I21" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>9</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="n">
         <v>529</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>289</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
       </c>
-      <c r="F22">
-        <v>3072</v>
-      </c>
-      <c r="G22">
-        <v>-10.338059907881945</v>
-      </c>
-      <c r="H22">
-        <v>-9.429296649709164</v>
-      </c>
-      <c r="I22">
-        <v>Inf</v>
+      <c r="F22" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-10.405890478431091</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-9.455746509153176</v>
+      </c>
+      <c r="I22" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>9</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="n">
         <v>576</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>289</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
       </c>
-      <c r="F23">
-        <v>3072</v>
-      </c>
-      <c r="G23">
-        <v>-9.936222293259458</v>
-      </c>
-      <c r="H23">
-        <v>-9.149244416127061</v>
-      </c>
-      <c r="I23">
-        <v>Inf</v>
+      <c r="F23" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-9.971087686947417</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-9.152046228001314</v>
+      </c>
+      <c r="I23" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>9</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="n">
         <v>625</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>289</v>
       </c>
       <c r="E24" t="s">
         <v>11</v>
       </c>
-      <c r="F24">
-        <v>3072</v>
-      </c>
-      <c r="G24">
-        <v>-10.115920547316463</v>
-      </c>
-      <c r="H24">
-        <v>-9.12118771730614</v>
-      </c>
-      <c r="I24">
-        <v>Inf</v>
+      <c r="F24" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-9.577264107727451</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-8.92614957612232</v>
+      </c>
+      <c r="I24" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>9</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="n">
         <v>676</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>289</v>
       </c>
       <c r="E25" t="s">
         <v>11</v>
       </c>
-      <c r="F25">
-        <v>3072</v>
-      </c>
-      <c r="G25">
-        <v>-10.22375713319279</v>
-      </c>
-      <c r="H25">
-        <v>-9.233054119392474</v>
-      </c>
-      <c r="I25">
-        <v>Inf</v>
+      <c r="F25" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-10.093986267089974</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-9.127320382721837</v>
+      </c>
+      <c r="I25" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>9</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="n">
         <v>729</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>289</v>
       </c>
       <c r="E26" t="s">
         <v>11</v>
       </c>
-      <c r="F26">
-        <v>3072</v>
-      </c>
-      <c r="G26">
-        <v>-9.922046489377843</v>
-      </c>
-      <c r="H26">
-        <v>-9.084209470002122</v>
-      </c>
-      <c r="I26">
-        <v>Inf</v>
+      <c r="F26" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-9.60361463807148</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-8.869562603027548</v>
+      </c>
+      <c r="I26" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>9</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="n">
         <v>784</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>289</v>
       </c>
       <c r="E27" t="s">
         <v>11</v>
       </c>
-      <c r="F27">
-        <v>3072</v>
-      </c>
-      <c r="G27">
-        <v>-9.864635682854987</v>
-      </c>
-      <c r="H27">
-        <v>-8.900167304676778</v>
-      </c>
-      <c r="I27">
-        <v>Inf</v>
+      <c r="F27" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-9.56025947415762</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-8.745454183369711</v>
+      </c>
+      <c r="I27" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
         <v>9</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="n">
         <v>841</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>289</v>
       </c>
       <c r="E28" t="s">
         <v>11</v>
       </c>
-      <c r="F28">
-        <v>3072</v>
-      </c>
-      <c r="G28">
-        <v>-9.854493867713682</v>
-      </c>
-      <c r="H28">
-        <v>-8.91848636635814</v>
-      </c>
-      <c r="I28">
-        <v>Inf</v>
+      <c r="F28" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-9.80873006564817</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-8.82345917097893</v>
+      </c>
+      <c r="I28" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
         <v>9</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="n">
         <v>900</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>289</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
       </c>
-      <c r="F29">
-        <v>3072</v>
-      </c>
-      <c r="G29">
-        <v>-9.465752667367429</v>
-      </c>
-      <c r="H29">
-        <v>-8.81095236963317</v>
-      </c>
-      <c r="I29">
-        <v>Inf</v>
+      <c r="F29" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-9.828616383875938</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-8.867148702102098</v>
+      </c>
+      <c r="I29" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
         <v>9</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="n">
         <v>961</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>289</v>
       </c>
       <c r="E30" t="s">
         <v>11</v>
       </c>
-      <c r="F30">
-        <v>3072</v>
-      </c>
-      <c r="G30">
-        <v>-9.807568837743043</v>
-      </c>
-      <c r="H30">
-        <v>-8.944315341374137</v>
-      </c>
-      <c r="I30">
-        <v>Inf</v>
+      <c r="F30" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-9.800724863437544</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-8.819860410291415</v>
+      </c>
+      <c r="I30" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
         <v>9</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="n">
         <v>1024</v>
       </c>
       <c r="C31" t="s">
         <v>10</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>289</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
       </c>
-      <c r="F31">
-        <v>3072</v>
-      </c>
-      <c r="G31">
-        <v>-9.653813190890922</v>
-      </c>
-      <c r="H31">
-        <v>-8.813150244158269</v>
-      </c>
-      <c r="I31">
-        <v>Inf</v>
+      <c r="F31" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-9.650903193130764</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-8.635418010115837</v>
+      </c>
+      <c r="I31" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
         <v>9</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="n">
         <v>1089</v>
       </c>
       <c r="C32" t="s">
         <v>10</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>289</v>
       </c>
       <c r="E32" t="s">
         <v>11</v>
       </c>
-      <c r="F32">
-        <v>3072</v>
-      </c>
-      <c r="G32">
-        <v>-10.095246622755445</v>
-      </c>
-      <c r="H32">
-        <v>-9.051860845806322</v>
-      </c>
-      <c r="I32">
-        <v>Inf</v>
+      <c r="F32" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-9.335439074464162</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-8.61967473788789</v>
+      </c>
+      <c r="I32" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
